--- a/artfynd/A 16288-2026 artfynd.xlsx
+++ b/artfynd/A 16288-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,118 +784,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>133020572</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57145</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Holmsjön, Holmsjön, Vstm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>489891</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6608611</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16288-2026 artfynd.xlsx
+++ b/artfynd/A 16288-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133021233</v>
+        <v>95683204</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmsjön, Holmsjön, Vstm</t>
+          <t>N Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489800</v>
+        <v>489950</v>
       </c>
       <c r="R2" t="n">
-        <v>6608673</v>
+        <v>6608603</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,15 +760,127 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133021233</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Holmsjön, Holmsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>489800</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6608673</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Lotta Sörman</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Lotta Sörman</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16288-2026 artfynd.xlsx
+++ b/artfynd/A 16288-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683204</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,8 +891,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133021233</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>